--- a/satisfaction_surveys/024_ice_skating_experience_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/024_ice_skating_experience_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'occasionaly'}</t>
+          <t>occasionaly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionaly'}</t>
+          <t>Occasionaly</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Almost always'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'recreational_skater'}</t>
+          <t>recreational_skater</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Recreational Skater'}</t>
+          <t>Recreational Skater</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'competitive_skater'}</t>
+          <t>competitive_skater</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Competitive Skater'}</t>
+          <t>Competitive Skater</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'recreational/competitive_skater'}</t>
+          <t>recreational/competitive_skater</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Recreational/Competitive Skater'}</t>
+          <t>Recreational/Competitive Skater</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'improve_my_skills'}</t>
+          <t>improve_my_skills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Improve my skills'}</t>
+          <t>Improve my skills</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'get_faster'}</t>
+          <t>get_faster</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Get faster'}</t>
+          <t>Get faster</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'have_fun'}</t>
+          <t>have_fun</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Have fun'}</t>
+          <t>Have fun</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'meet_new_people'}</t>
+          <t>meet_new_people</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Meet new people'}</t>
+          <t>Meet new people</t>
         </is>
       </c>
     </row>
